--- a/questionnaire_templates/009_new_product_taste_preferences_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/009_new_product_taste_preferences_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Product Name</t>
+          <t>Product Name Hint</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Product Rating Hint</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Time To Complete Hint</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -763,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email Hint</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Phone Hint</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Date Hint</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Time Hint</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Product Name Hint 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Taste Preferences 2 Hint</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Product Rating 2 Hint</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Time To Complete 2 Hint</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
